--- a/Framework_MWC_Testing/data/ai_processed/register/RegisterData.xlsx
+++ b/Framework_MWC_Testing/data/ai_processed/register/RegisterData.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,12 +474,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>password123</t>
+          <t>Abcdefg1!</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>password123</t>
+          <t>Abcdefg1!</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,18 +496,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>testuser123</t>
+          <t>AnhDuong11</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>password123</t>
+          <t>Abcdefg1!</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>password123</t>
+          <t>Abcdefg1!</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -524,27 +524,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>testuser123</t>
+          <t>AnhDuong11</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>987654321</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>password123</t>
-        </is>
-      </c>
+          <t>0987654321</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>password123</t>
+          <t>Abcdefg1!</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Số điện thoại không đúng định dạng!</t>
+          <t>Vui lòng điền vào trường này</t>
         </is>
       </c>
     </row>
@@ -556,7 +552,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>testuser123</t>
+          <t>AnhDuong11</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -566,17 +562,13 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>passwrd</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>passwrd</t>
-        </is>
-      </c>
+          <t>Abcdefg1!</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mật khẩu phải lớn hơn 8 ký tự và nhỏ hơn 20 ký tự!</t>
+          <t>Vui lòng điền vào trường này</t>
         </is>
       </c>
     </row>
@@ -588,7 +580,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>testuser123</t>
+          <t>AnhDuong11</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -598,17 +590,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>password12345678901234567890</t>
+          <t>Abcdefg1!</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>password12345678901234567890</t>
+          <t>Abcdefg1!</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mật khẩu phải lớn hơn 8 ký tự và nhỏ hơn 20 ký tự!</t>
+          <t>tài khoản đã tồn tại trong hệ thống</t>
         </is>
       </c>
     </row>
@@ -620,27 +612,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>testuser123</t>
+          <t>AnhDuong12</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0987654321</t>
+          <t>9876543210</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>password123</t>
+          <t>Abcdefg1!</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>password1234</t>
+          <t>Abcdefg1!</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>mật khẩu không giống nhau</t>
+          <t>Số điện thoại không đúng định dạng!</t>
         </is>
       </c>
     </row>
@@ -652,7 +644,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AnhDuong11</t>
+          <t>AnhDuong13</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -662,17 +654,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>password123</t>
+          <t>Abcdefg</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>password123</t>
+          <t>Abcdefg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>tài khoản đã tồn tại trong hệ thống</t>
+          <t>Mật khẩu phải lớn hơn 8 ký tự và nhỏ hơn 20 ký tự!</t>
         </is>
       </c>
     </row>
@@ -684,7 +676,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>testuser123456789</t>
+          <t>AnhDuong14</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -694,17 +686,81 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>password12345678</t>
+          <t>Abcdefg1!Abcdefg1!</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>password12345678</t>
+          <t>Abcdefg1!Abcdefg1!</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>testuser123456789</t>
+          <t>Mật khẩu phải lớn hơn 8 ký tự và nhỏ hơn 20 ký tự!</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>RG09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>AnhDuong15</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0987654321</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Abcdefg1!</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Abcdefg</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>mật khẩu không giống nhau</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>RG10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>AnhDuong16</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0987654321</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Abcdefg1!</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Abcdefg1!</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>AnhDuong16</t>
         </is>
       </c>
     </row>

--- a/Framework_MWC_Testing/data/ai_processed/register/RegisterData.xlsx
+++ b/Framework_MWC_Testing/data/ai_processed/register/RegisterData.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,7 +496,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AnhDuong11</t>
+          <t>testuser123</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
@@ -524,7 +524,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AnhDuong11</t>
+          <t>testuser123</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AnhDuong11</t>
+          <t>testuser123</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -580,12 +580,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AnhDuong11</t>
+          <t>testuser123</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0987654321</t>
+          <t>987654321</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>tài khoản đã tồn tại trong hệ thống</t>
+          <t>Số điện thoại không đúng định dạng!</t>
         </is>
       </c>
     </row>
@@ -612,27 +612,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AnhDuong12</t>
+          <t>testuser123</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>9876543210</t>
+          <t>0987654321</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Abcdefg1!</t>
+          <t>Abcdefg</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Abcdefg1!</t>
+          <t>Abcdefg</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Số điện thoại không đúng định dạng!</t>
+          <t>Mật khẩu phải có ít nhất 8 ký tự!</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AnhDuong13</t>
+          <t>testuser123</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -654,17 +654,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Abcdefg</t>
+          <t>Abcdefg1!Abcdefg1!Abcdefg1!</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Abcdefg</t>
+          <t>Abcdefg1!Abcdefg1!Abcdefg1!</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mật khẩu phải lớn hơn 8 ký tự và nhỏ hơn 20 ký tự!</t>
+          <t>Mật khẩu phải có không quá 20 ký tự!</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AnhDuong14</t>
+          <t>testuser123</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -686,17 +686,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Abcdefg1!Abcdefg1!</t>
+          <t>Abcdefg1!</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Abcdefg1!Abcdefg1!</t>
+          <t>Abcdefg</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mật khẩu phải lớn hơn 8 ký tự và nhỏ hơn 20 ký tự!</t>
+          <t>Xác nhận mật khẩu không khớp!</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AnhDuong15</t>
+          <t>tstusr</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -723,12 +723,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Abcdefg</t>
+          <t>Abcdefg1!</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>mật khẩu không giống nhau</t>
+          <t>Tên người dùng phải có ít nhất 8 ký tự!</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AnhDuong16</t>
+          <t>testuser12345678901234567890</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -760,7 +760,71 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AnhDuong16</t>
+          <t>Tên người dùng phải có không quá 20 ký tự!</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>RG11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>testuser123</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0987654321</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Abcdefg</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Abcdefg</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Mật khẩu phải có ít nhất 8 ký tự!</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>RG12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>testuser123</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0987654321</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Abcdefg1!Abc</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Abcdefg1!Abc</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Mật khẩu phải có không quá 20 ký tự!</t>
         </is>
       </c>
     </row>

--- a/Framework_MWC_Testing/data/ai_processed/register/RegisterData.xlsx
+++ b/Framework_MWC_Testing/data/ai_processed/register/RegisterData.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,11 @@
           <t>RG01</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>testuser</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>0987654321</t>
@@ -474,17 +478,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Abcdefg1!</t>
+          <t>password123</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Abcdefg1!</t>
+          <t>password123</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vui lòng điền vào trường này</t>
+          <t>Đăng ký thành công</t>
         </is>
       </c>
     </row>
@@ -494,20 +498,20 @@
           <t>RG02</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>testuser123</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0987654321</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Abcdefg1!</t>
+          <t>password123</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Abcdefg1!</t>
+          <t>password123</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -524,18 +528,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>testuser123</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>0987654321</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>testuser</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>password123</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Abcdefg1!</t>
+          <t>password123</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -552,7 +556,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>testuser123</t>
+          <t>testuser</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -560,12 +564,12 @@
           <t>0987654321</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Abcdefg1!</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>password123</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>Vui lòng điền vào trường này</t>
@@ -580,27 +584,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>testuser123</t>
+          <t>testuser</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>987654321</t>
+          <t>0987654321</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Abcdefg1!</t>
+          <t>password123</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Abcdefg1!</t>
+          <t>wrongpassword</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Số điện thoại không đúng định dạng!</t>
+          <t>Mật khẩu không khớp</t>
         </is>
       </c>
     </row>
@@ -612,27 +616,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>testuser123</t>
+          <t>testuser</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0987654321</t>
+          <t>1234567890</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Abcdefg</t>
+          <t>password123</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Abcdefg</t>
+          <t>password123</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mật khẩu phải có ít nhất 8 ký tự!</t>
+          <t>Số điện thoại không hợp lệ</t>
         </is>
       </c>
     </row>
@@ -644,27 +648,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>testuser123</t>
+          <t>testuser</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0987654321</t>
+          <t>123456789</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Abcdefg1!Abcdefg1!Abcdefg1!</t>
+          <t>password123</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Abcdefg1!Abcdefg1!Abcdefg1!</t>
+          <t>password123</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mật khẩu phải có không quá 20 ký tự!</t>
+          <t>Số điện thoại không hợp lệ</t>
         </is>
       </c>
     </row>
@@ -676,7 +680,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>testuser123</t>
+          <t>testuser</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -686,145 +690,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Abcdefg1!</t>
+          <t>passwor</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Abcdefg</t>
+          <t>passwor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Xác nhận mật khẩu không khớp!</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>RG09</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>tstusr</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>0987654321</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Abcdefg1!</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Abcdefg1!</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Tên người dùng phải có ít nhất 8 ký tự!</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>RG10</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>testuser12345678901234567890</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>0987654321</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Abcdefg1!</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Abcdefg1!</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Tên người dùng phải có không quá 20 ký tự!</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>RG11</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>testuser123</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>0987654321</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Abcdefg</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Abcdefg</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Mật khẩu phải có ít nhất 8 ký tự!</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>RG12</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>testuser123</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>0987654321</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Abcdefg1!Abc</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Abcdefg1!Abc</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Mật khẩu phải có không quá 20 ký tự!</t>
+          <t>Mật khẩu phải từ 8 đến 20 ký tự</t>
         </is>
       </c>
     </row>

--- a/Framework_MWC_Testing/data/ai_processed/register/RegisterData.xlsx
+++ b/Framework_MWC_Testing/data/ai_processed/register/RegisterData.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,17 +469,17 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0987654321</t>
+          <t>0123456789</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>password123</t>
+          <t>Aa1!aaaaaa</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>password123</t>
+          <t>Aa1!aaaaaa</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,18 +496,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>user123</t>
+          <t>testuser123</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>password123</t>
+          <t>Aa1!aaaaaa</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>password123</t>
+          <t>Aa1!aaaaaa</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -524,18 +524,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>user123</t>
+          <t>testuser123</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0987654321</t>
+          <t>0123456789</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>password123</t>
+          <t>Aa1!aaaaaa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -552,17 +552,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>user123</t>
+          <t>testuser123</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0987654321</t>
+          <t>0123456789</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>password123</t>
+          <t>Aa1!aaaaaa</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -580,27 +580,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>user123</t>
+          <t>AnhDuong11</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>123456789</t>
+          <t>0123456789</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>password123</t>
+          <t>Aa1!aaaaaa</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>password123</t>
+          <t>Aa1!aaaaaa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Số điện thoại không hợp lệ</t>
+          <t>tài khoản đã tồn tại trong hệ thống</t>
         </is>
       </c>
     </row>
@@ -612,27 +612,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>user123</t>
+          <t>testuser123</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0987654321</t>
+          <t>9876543210</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>Aa1!aaaaaa</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>Aa1!aaaaaa</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mật khẩu phải từ 8 đến 20 ký tự</t>
+          <t>Số điện thoại không hợp lệ</t>
         </is>
       </c>
     </row>
@@ -644,27 +644,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>user123</t>
+          <t>testuser123</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0987654321</t>
+          <t>0a123456789</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>password123</t>
+          <t>Aa1!aaaaaa</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>wrongpass</t>
+          <t>Aa1!aaaaaa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mật khẩu không khớp</t>
+          <t>Số điện thoại không hợp lệ</t>
         </is>
       </c>
     </row>
@@ -676,27 +676,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>user123</t>
+          <t>testuser123</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0987654321</t>
+          <t>0@123456789</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>passw</t>
+          <t>Aa1!aaaaaa</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>passw</t>
+          <t>Aa1!aaaaaa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mật khẩu phải từ 8 đến 20 ký tự</t>
+          <t>Số điện thoại không hợp lệ</t>
         </is>
       </c>
     </row>
@@ -708,27 +708,155 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>user123</t>
+          <t>testuser123</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0987654321</t>
+          <t>0 123456789</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>password12345678901234567890</t>
+          <t>Aa1!aaaaaa</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>password12345678901234567890</t>
+          <t>Aa1!aaaaaa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>Số điện thoại không hợp lệ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>RG10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>testuser123</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0123456789</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Aa1!aaa</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Aa1!aaa</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>Mật khẩu phải từ 8 đến 20 ký tự</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>RG11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>testuser123</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0123456789</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Aa1!aaaaaaaab</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Aa1!aaaaaaaab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Mật khẩu phải từ 8 đến 20 ký tự</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>RG12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>testuser123</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0123456789</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Aa1!aaaaaa</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Bb2@bbbbbb</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Mật khẩu không khớp</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>RG13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>testuser124</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0123456789</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Aa1!aaaaaa</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Aa1!aaaaaa</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>testuser124</t>
         </is>
       </c>
     </row>

--- a/Framework_MWC_Testing/data/ai_processed/register/RegisterData.xlsx
+++ b/Framework_MWC_Testing/data/ai_processed/register/RegisterData.xlsx
@@ -469,17 +469,17 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0123456789</t>
+          <t>0987654321</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Aa1!aaaaaa</t>
+          <t>password123</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aa1!aaaaaa</t>
+          <t>password123</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,18 +496,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>testuser123</t>
+          <t>newuser123</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Aa1!aaaaaa</t>
+          <t>password123</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aa1!aaaaaa</t>
+          <t>password123</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -524,20 +524,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>testuser123</t>
+          <t>newuser123</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0123456789</t>
+          <t>0987654321</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Aa1!aaaaaa</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>Vui lòng điền vào trường này</t>
@@ -552,17 +548,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>testuser123</t>
+          <t>newuser123</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0123456789</t>
+          <t>0987654321</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Aa1!aaaaaa</t>
+          <t>password123</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -585,17 +581,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0123456789</t>
+          <t>0987654321</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Aa1!aaaaaa</t>
+          <t>password123</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aa1!aaaaaa</t>
+          <t>password123</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -612,22 +608,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>testuser123</t>
+          <t>newuser123</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>9876543210</t>
+          <t>987654321</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Aa1!aaaaaa</t>
+          <t>password123</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aa1!aaaaaa</t>
+          <t>password123</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -644,22 +640,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>testuser123</t>
+          <t>newuser123</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0a123456789</t>
+          <t>0a87654321</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Aa1!aaaaaa</t>
+          <t>password123</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aa1!aaaaaa</t>
+          <t>password123</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -676,22 +672,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>testuser123</t>
+          <t>newuser123</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0@123456789</t>
+          <t>098765432a</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Aa1!aaaaaa</t>
+          <t>password123</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aa1!aaaaaa</t>
+          <t>password123</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -708,22 +704,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>testuser123</t>
+          <t>newuser123</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0 123456789</t>
+          <t>09876 54321</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Aa1!aaaaaa</t>
+          <t>password123</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aa1!aaaaaa</t>
+          <t>password123</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -740,22 +736,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>testuser123</t>
+          <t>newuser123</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0123456789</t>
+          <t>0987654321</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Aa1!aaa</t>
+          <t>pass123</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aa1!aaa</t>
+          <t>pass123</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -772,22 +768,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>testuser123</t>
+          <t>newuser123</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0123456789</t>
+          <t>0987654321</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Aa1!aaaaaaaab</t>
+          <t>password12345678901234567890</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aa1!aaaaaaaab</t>
+          <t>password12345678901234567890</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -804,22 +800,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>testuser123</t>
+          <t>newuser123</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0123456789</t>
+          <t>0987654321</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Aa1!aaaaaa</t>
+          <t>password123</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bb2@bbbbbb</t>
+          <t>password1234</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -836,27 +832,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>testuser124</t>
+          <t>newuser123</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0123456789</t>
+          <t>0987654321</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Aa1!aaaaaa</t>
+          <t>password123</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aa1!aaaaaa</t>
+          <t>password123</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>testuser124</t>
+          <t>newuser123</t>
         </is>
       </c>
     </row>

--- a/Framework_MWC_Testing/data/ai_processed/register/RegisterData.xlsx
+++ b/Framework_MWC_Testing/data/ai_processed/register/RegisterData.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>newuser123</t>
+          <t>testuser123</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
@@ -524,7 +524,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>newuser123</t>
+          <t>testuser123</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -533,7 +533,11 @@
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>password123</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>Vui lòng điền vào trường này</t>
@@ -548,7 +552,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>newuser123</t>
+          <t>testuser123</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -608,7 +612,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>newuser123</t>
+          <t>testuser123</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -640,7 +644,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>newuser123</t>
+          <t>testuser123</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -672,7 +676,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>newuser123</t>
+          <t>testuser123</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -704,12 +708,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>newuser123</t>
+          <t>testuser123</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>09876 54321</t>
+          <t>0987654 321</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -736,7 +740,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>newuser123</t>
+          <t>testuser123</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -746,12 +750,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>pass123</t>
+          <t>passwrd</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>pass123</t>
+          <t>passwrd</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -768,7 +772,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>newuser123</t>
+          <t>testuser123</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -800,7 +804,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>newuser123</t>
+          <t>testuser123</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -832,7 +836,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>newuser123</t>
+          <t>testuser123</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -852,7 +856,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>newuser123</t>
+          <t>testuser123</t>
         </is>
       </c>
     </row>

--- a/Framework_MWC_Testing/data/ai_processed/register/RegisterData.xlsx
+++ b/Framework_MWC_Testing/data/ai_processed/register/RegisterData.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,10 +463,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RG01</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>TestUser123</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>0987654321</t>
@@ -474,40 +478,40 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>password123</t>
+          <t>abcde1234</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>password123</t>
+          <t>abcde1234</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vui lòng điền vào trường này</t>
+          <t>TestUser123</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>RG02</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>testuser123</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0987654321</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>password123</t>
+          <t>abcde1234</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>password123</t>
+          <t>abcde1234</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -519,12 +523,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RG03</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>testuser123</t>
+          <t>AnhDuong11</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -532,331 +536,207 @@
           <t>0987654321</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>abcde1234</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>password123</t>
+          <t>abcde1234</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vui lòng điền vào trường này</t>
+          <t>tài khoản đã tồn tại trong hệ thống</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RG04</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>testuser123</t>
+          <t>TestUser123</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0987654321</t>
+          <t>098765432</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>password123</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
+          <t>abcde1234</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>abcde1234</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vui lòng điền vào trường này</t>
+          <t>Vui lòng điền đúng định dạng số điện thoại (10 chữ số).</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>RG05</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AnhDuong11</t>
+          <t>TestUser123</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0987654321</t>
+          <t>09876543210</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>password123</t>
+          <t>abcde1234</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>password123</t>
+          <t>abcde1234</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>tài khoản đã tồn tại trong hệ thống</t>
+          <t>Vui lòng điền đúng định dạng số điện thoại (10 chữ số).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>RG06</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>testuser123</t>
+          <t>TestUser123</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>987654321</t>
+          <t>0987654321</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>password123</t>
+          <t>abcde123</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>password123</t>
+          <t>abcde123</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Số điện thoại không hợp lệ</t>
+          <t>Mật khẩu phải từ 8 đến 20 ký tự.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RG07</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>testuser123</t>
+          <t>TestUser123</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0a87654321</t>
+          <t>0987654321</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>password123</t>
+          <t>abcde12345678901234567890</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>password123</t>
+          <t>abcde12345678901234567890</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Số điện thoại không hợp lệ</t>
+          <t>Mật khẩu phải từ 8 đến 20 ký tự.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>RG08</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>testuser123</t>
+          <t>TestUser123</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>098765432a</t>
+          <t>0987654321</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>password123</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>password123</t>
-        </is>
-      </c>
+          <t>abcde1234</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Số điện thoại không hợp lệ</t>
+          <t>Vui lòng điền vào trường này</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>RG09</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>testuser123</t>
+          <t>TestUser123</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0987654 321</t>
+          <t>0987654321</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>password123</t>
+          <t>abcde1234</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>password123</t>
+          <t>abcde12345</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Số điện thoại không hợp lệ</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>RG10</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>testuser123</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>0987654321</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>passwrd</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>passwrd</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Mật khẩu phải từ 8 đến 20 ký tự</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>RG11</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>testuser123</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>0987654321</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>password12345678901234567890</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>password12345678901234567890</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Mật khẩu phải từ 8 đến 20 ký tự</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>RG12</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>testuser123</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>0987654321</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>password123</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>password1234</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Mật khẩu không khớp</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>RG13</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>testuser123</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>0987654321</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>password123</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>password123</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>testuser123</t>
+          <t>Mật khẩu xác nhận không khớp với mật khẩu.</t>
         </is>
       </c>
     </row>

--- a/Framework_MWC_Testing/data/ai_processed/register/RegisterData.xlsx
+++ b/Framework_MWC_Testing/data/ai_processed/register/RegisterData.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,11 +466,7 @@
           <t>RG01</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>NewUser123</t>
-        </is>
-      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>0123456789</t>
@@ -478,17 +474,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1234567890</t>
+          <t>Pass1234567890</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1234567890</t>
+          <t>Pass1234567890</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dữ liệu hợp lệ</t>
+          <t>Vui lòng điền vào trường này</t>
         </is>
       </c>
     </row>
@@ -503,24 +499,20 @@
           <t>NewUser123</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>0123456789</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>12345678</t>
+          <t>Pass1234567890</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>12345678</t>
+          <t>Pass1234567890</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dữ liệu hợp lệ</t>
+          <t>Vui lòng điền vào trường này</t>
         </is>
       </c>
     </row>
@@ -540,19 +532,15 @@
           <t>0123456789</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>123456789</t>
-        </is>
-      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>123456789</t>
+          <t>Pass1234567890</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dữ liệu hợp lệ</t>
+          <t>Vui lòng điền vào trường này</t>
         </is>
       </c>
     </row>
@@ -574,17 +562,13 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>12345678901234567890</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>12345678901234567890</t>
-        </is>
-      </c>
+          <t>Pass1234567890</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dữ liệu hợp lệ</t>
+          <t>Vui lòng điền vào trường này</t>
         </is>
       </c>
     </row>
@@ -606,17 +590,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>123456789012345678901</t>
+          <t>Pass1234567890</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>123456789012345678901</t>
+          <t>Pass1234567890</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dữ liệu hợp lệ</t>
+          <t>NewUser123</t>
         </is>
       </c>
     </row>
@@ -626,7 +610,11 @@
           <t>RG06</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>NewUser123</t>
+        </is>
+      </c>
       <c r="C7" t="inlineStr">
         <is>
           <t>0123456789</t>
@@ -634,17 +622,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1234567890</t>
+          <t>Pass1234</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1234567890</t>
+          <t>Pass1234</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vui lòng điền vào trường này</t>
+          <t>NewUser123</t>
         </is>
       </c>
     </row>
@@ -659,20 +647,24 @@
           <t>NewUser123</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0123456789</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1234567890</t>
+          <t>Pass12345</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1234567890</t>
+          <t>Pass12345</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vui lòng điền vào trường này</t>
+          <t>NewUser123</t>
         </is>
       </c>
     </row>
@@ -692,15 +684,19 @@
           <t>0123456789</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Pass1234567890123456789</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1234567890</t>
+          <t>Pass1234567890123456789</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vui lòng điền vào trường này</t>
+          <t>NewUser123</t>
         </is>
       </c>
     </row>
@@ -722,353 +718,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1234567890</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
+          <t>Pass12345678901234567890</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Pass12345678901234567890</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vui lòng điền vào trường này</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>RG10</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>NewUser123</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>012345678</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>1234567890</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>1234567890</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Số điện thoại không hợp lệ</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>RG11</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>NewUser123</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>01234567890</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>1234567890</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>1234567890</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Số điện thoại không hợp lệ</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>RG12</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>NewUser123</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1234567890</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>1234567890</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>1234567890</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Số điện thoại không hợp lệ</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>RG13</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>NewUser123</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>0123a56789</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>1234567890</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>1234567890</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Số điện thoại không hợp lệ</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>RG14</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>NewUser123</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>0123!56789</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>1234567890</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>1234567890</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Số điện thoại không hợp lệ</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>RG15</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>NewUser123</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>0123 56789</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>1234567890</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>1234567890</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Số điện thoại không hợp lệ</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>RG16</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>NewUser123</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>0123456789</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>1234567</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>1234567890</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Mật khẩu phải từ 8 đến 20 ký tự</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>RG17</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>NewUser123</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>0123456789</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>1234567890123456789012</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>1234567890</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Mật khẩu phải từ 8 đến 20 ký tự</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>RG18</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>NewUser123</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>0123456789</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>1234567890</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>12345678901</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Mật khẩu không khớp</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>RG19</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>AnhDuong11</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>0123456789</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>1234567890</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>1234567890</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>tài khoản đã tồn tại trong hệ thống</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>RG20</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Vui lòng điền vào trường này</t>
+          <t>NewUser123</t>
         </is>
       </c>
     </row>

--- a/Framework_MWC_Testing/data/ai_processed/register/RegisterData.xlsx
+++ b/Framework_MWC_Testing/data/ai_processed/register/RegisterData.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,10 +463,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RG01</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
+          <t>T001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>NewUser123</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>0123456789</t>
@@ -474,40 +478,40 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Pass1234567890</t>
+          <t>Pass1234</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Pass1234567890</t>
+          <t>Pass1234</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vui lòng điền vào trường này</t>
+          <t>NewUser123</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>RG02</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>NewUser123</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>T002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0123456789</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Pass1234567890</t>
+          <t>Pass1234</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Pass1234567890</t>
+          <t>Pass1234</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -519,12 +523,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RG03</t>
+          <t>T003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NewUser123</t>
+          <t>AnhDuong11</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -532,22 +536,26 @@
           <t>0123456789</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Pass1234</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Pass1234567890</t>
+          <t>Pass1234</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vui lòng điền vào trường này</t>
+          <t>tài khoản đã tồn tại trong hệ thống</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RG04</t>
+          <t>T004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -555,17 +563,17 @@
           <t>NewUser123</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>0123456789</t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Pass1234567890</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
+          <t>Pass1234</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Pass1234</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>Vui lòng điền vào trường này</t>
@@ -575,7 +583,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>RG05</t>
+          <t>T005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -585,29 +593,29 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0123456789</t>
+          <t>012345678</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Pass1234567890</t>
+          <t>Pass1234</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pass1234567890</t>
+          <t>Pass1234</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>NewUser123</t>
+          <t>Số điện thoại không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>RG06</t>
+          <t>T006</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -617,7 +625,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0123456789</t>
+          <t>01234567890</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -632,14 +640,14 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>NewUser123</t>
+          <t>Số điện thoại không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RG07</t>
+          <t>T007</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -649,29 +657,29 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0123456789</t>
+          <t>1234567890</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Pass12345</t>
+          <t>Pass1234</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pass12345</t>
+          <t>Pass1234</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>NewUser123</t>
+          <t>Số điện thoại không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>RG08</t>
+          <t>T008</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -681,29 +689,29 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0123456789</t>
+          <t>01234a6789</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Pass1234567890123456789</t>
+          <t>Pass1234</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Pass1234567890123456789</t>
+          <t>Pass1234</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>NewUser123</t>
+          <t>Số điện thoại không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>RG09</t>
+          <t>T009</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -713,22 +721,206 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>01234!6789</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Pass1234</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Pass1234</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Số điện thoại không hợp lệ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>T010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>NewUser123</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>01234 6789</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Pass1234</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Pass1234</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Số điện thoại không hợp lệ</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>T011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>NewUser123</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t>0123456789</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Pass12345678901234567890</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Pass12345678901234567890</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>NewUser123</t>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Pass1234</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vui lòng điền vào trường này</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>T012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>NewUser123</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0123456789</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Pass123</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Pass123</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Mật khẩu phải từ 8 đến 20 ký tự</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>T013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>NewUser123</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0123456789</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Pass12345678901234567</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Pass12345678901234567</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Mật khẩu phải từ 8 đến 20 ký tự</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>T014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>NewUser123</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0123456789</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Pass1234</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vui lòng điền vào trường này</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>T015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>NewUser123</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0123456789</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Pass1234</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Pass12345678901</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Mật khẩu không khớp</t>
         </is>
       </c>
     </row>
